--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5a35b009a80b462a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R56338de2d5614c7d"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R56338de2d5614c7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4a7458f7e60f433a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4a7458f7e60f433a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R09fe663a27bc4770"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R09fe663a27bc4770"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R66dc9158455847bd"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R66dc9158455847bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Reea22e0d88cc4f86"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Reea22e0d88cc4f86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rffdb3aca5e5f4a32"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rffdb3aca5e5f4a32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R78c081b7a1344411"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R78c081b7a1344411"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra4c97bb59b5d4a88"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra4c97bb59b5d4a88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3730824531fa4be0"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3730824531fa4be0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R651adb6da1834c6e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R651adb6da1834c6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5e292aaf287642f4"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5e292aaf287642f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfdd8e30918d24df7"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfdd8e30918d24df7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rac079c0671824aae"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rac079c0671824aae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rae377d6fa86f4c1d"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rae377d6fa86f4c1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re92cd0a0bd074eb0"/>
   </x:sheets>
 </x:workbook>
 </file>
